--- a/artfynd/A 20971-2026 artfynd.xlsx
+++ b/artfynd/A 20971-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,2605 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135140404</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>499857</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6619540</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack med savflöde på gran. Märkt med rött band. Svårt att se på fotot då det inte är bra fotoljus.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135140453</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>499862</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6619534</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på gran märkt med rött band.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135140509</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>499863</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6619536</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på gran märkt med rött band.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135140614</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>499866</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6619553</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på gran märkt med rött band.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135140687</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>499866</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6619546</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran märkt med rött band.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135140904</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>499862</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6619539</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på gran märkt med rött band.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135140979</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>499837</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6619554</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på gran märkt med rött band. Svårt att se på fotot då det inte är bra fotoljus.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135141009</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>499842</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6619553</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran märkt med rött band.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135141163</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>499851</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6619510</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på gran märkt med rött band.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135141224</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>499870</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6619510</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på gran märkt med rött band.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135141264</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>499849</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6619491</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på gran märkt med rött band.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135141395</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>499855</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6619492</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran märkt med rött band.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135141426</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>499849</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6619475</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på gran märkt med rött band. Äldre ringhack långt ner.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135139808</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långa mossen, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>499892</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6619299</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder fr tupp.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135141086</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>499844</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6619549</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135141328</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>499847</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6619490</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fjäder i bälgrop</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135152867</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långa mossen, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>500008</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6619349</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135152888</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långa mossen, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>499952</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6619392</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>på sten</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135139698</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långa mossen, Långa mossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>499893</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6619284</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135139951</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långa mossen, Långa mossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>499899</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6619315</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135139985</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långa mossen, Långa mossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>499899</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6619335</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135139940</v>
+      </c>
+      <c r="B25" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långa mossen, Långa mossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>499888</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6619305</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20971-2026 artfynd.xlsx
+++ b/artfynd/A 20971-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3025,10 +3025,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135139698</v>
+        <v>135280779</v>
       </c>
       <c r="B22" t="n">
-        <v>99112</v>
+        <v>57162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,48 +3036,48 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långa mossen, Långa mossen, Vstm</t>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499893</v>
+        <v>499884</v>
       </c>
       <c r="R22" t="n">
-        <v>6619284</v>
+        <v>6619468</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3104,22 +3104,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3134,19 +3134,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135139951</v>
+        <v>135139698</v>
       </c>
       <c r="B23" t="n">
         <v>99112</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499899</v>
+        <v>499893</v>
       </c>
       <c r="R23" t="n">
-        <v>6619315</v>
+        <v>6619284</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3267,7 +3267,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135139985</v>
+        <v>135139951</v>
       </c>
       <c r="B24" t="n">
         <v>99112</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3319,7 +3319,7 @@
         <v>499899</v>
       </c>
       <c r="R24" t="n">
-        <v>6619335</v>
+        <v>6619315</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3388,10 +3388,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135139940</v>
+        <v>135139985</v>
       </c>
       <c r="B25" t="n">
-        <v>111153</v>
+        <v>99112</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,36 +3399,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220240</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499888</v>
+        <v>499899</v>
       </c>
       <c r="R25" t="n">
-        <v>6619305</v>
+        <v>6619335</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3482,12 +3482,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3511,6 +3506,132 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135139940</v>
+      </c>
+      <c r="B26" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långa mossen, Långa mossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>499888</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6619305</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20971-2026 artfynd.xlsx
+++ b/artfynd/A 20971-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135068435</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135068477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135140404</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135140453</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,6 +1291,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135140509</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,6 +1413,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135140614</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135140687</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1617,6 +1657,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135140904</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1737,6 +1782,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135140979</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1854,6 +1904,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141009</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1971,6 +2026,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141163</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2088,6 +2148,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141224</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2205,6 +2270,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141264</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2322,6 +2392,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141395</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2439,6 +2514,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141426</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2570,6 +2650,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135139808</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2682,6 +2767,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141086</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2813,6 +2903,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141328</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2915,6 +3010,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152867</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3022,6 +3122,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152888</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3143,6 +3248,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135280779</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3264,6 +3374,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135139698</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3385,6 +3500,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135139951</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3506,6 +3626,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135139985</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3632,8 +3757,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135139940</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 20971-2026 artfynd.xlsx
+++ b/artfynd/A 20971-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135068435</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>135068477</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>135140404</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>135140453</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>135140509</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>135140614</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>135140687</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>135140904</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>135140979</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135141009</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135141163</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135141224</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135141264</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135141395</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>135141426</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>135139808</v>
       </c>
       <c r="B17" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>135141086</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>135141328</v>
       </c>
       <c r="B19" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>135152867</v>
       </c>
       <c r="B20" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>135152888</v>
       </c>
       <c r="B21" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>135280779</v>
       </c>
       <c r="B22" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135139698</v>
       </c>
       <c r="B23" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>135139951</v>
       </c>
       <c r="B24" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>135139985</v>
       </c>
       <c r="B25" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>135139940</v>
       </c>
       <c r="B26" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 20971-2026 artfynd.xlsx
+++ b/artfynd/A 20971-2026 artfynd.xlsx
@@ -3259,7 +3259,7 @@
         <v>135139698</v>
       </c>
       <c r="B23" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>135139951</v>
       </c>
       <c r="B24" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>135139985</v>
       </c>
       <c r="B25" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>135139940</v>
       </c>
       <c r="B26" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 20971-2026 artfynd.xlsx
+++ b/artfynd/A 20971-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3130,10 +3130,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135139698</v>
+        <v>135280779</v>
       </c>
       <c r="B22" t="n">
-        <v>99186</v>
+        <v>57167</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3141,48 +3141,48 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långa mossen, Långa mossen, Vstm</t>
+          <t>Brattahällskogen, Brattahällskogen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499893</v>
+        <v>499884</v>
       </c>
       <c r="R22" t="n">
-        <v>6619284</v>
+        <v>6619468</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3209,22 +3209,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3239,24 +3239,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135139698</t>
+          <t>https://artportalen.se/Sighting/135280779</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135139951</v>
+        <v>135139698</v>
       </c>
       <c r="B23" t="n">
         <v>99186</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3305,10 +3305,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499899</v>
+        <v>499893</v>
       </c>
       <c r="R23" t="n">
-        <v>6619315</v>
+        <v>6619284</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3376,13 +3376,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135139951</t>
+          <t>https://artportalen.se/Sighting/135139698</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135139985</v>
+        <v>135139951</v>
       </c>
       <c r="B24" t="n">
         <v>99186</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3434,7 +3434,7 @@
         <v>499899</v>
       </c>
       <c r="R24" t="n">
-        <v>6619335</v>
+        <v>6619315</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3502,16 +3502,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135139985</t>
+          <t>https://artportalen.se/Sighting/135139951</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135139940</v>
+        <v>135139985</v>
       </c>
       <c r="B25" t="n">
-        <v>111237</v>
+        <v>99186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3519,36 +3519,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220240</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499888</v>
+        <v>499899</v>
       </c>
       <c r="R25" t="n">
-        <v>6619305</v>
+        <v>6619335</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3602,12 +3602,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3632,6 +3627,137 @@
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135139985</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135139940</v>
+      </c>
+      <c r="B26" t="n">
+        <v>111237</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långa mossen, Långa mossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>499888</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6619305</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135139940</t>
         </is>
@@ -3663,6 +3789,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
